--- a/project_final_testcase/30_Defects_Tracker.xlsx
+++ b/project_final_testcase/30_Defects_Tracker.xlsx
@@ -398,6 +398,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I31"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="25.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="35.83203125" customWidth="1"/>
+    <col min="8" max="8" width="25.83203125" customWidth="1"/>
+    <col min="9" max="9" width="75.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -709,13 +720,13 @@
         <v>FAIL</v>
       </c>
       <c r="G11" t="str">
-        <v>Infrastructure / Rate-Limit Blocker</v>
+        <v>Test Setup / Automation Failure</v>
       </c>
       <c r="H11" t="str">
         <v>vercel-final-audit.json</v>
       </c>
       <c r="I11" t="str">
-        <v>UI NavbarSearch Enter timeout 60000ms</v>
+        <v>UI NavbarSearch Enter timeout 60000ms (Playwright locator timeout; unverified infrastructure hypothesis)</v>
       </c>
     </row>
     <row r="12">
